--- a/hardware/bom/RescueSwarm_University_Funding_Request.xlsx
+++ b/hardware/bom/RescueSwarm_University_Funding_Request.xlsx
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>824072</v>
+        <v>737829</v>
       </c>
       <c r="C6" s="7" t="inlineStr"/>
       <c r="D6" s="7" t="inlineStr"/>
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>698101</v>
+        <v>683306</v>
       </c>
       <c r="C7" s="9" t="inlineStr"/>
       <c r="D7" s="9" t="inlineStr"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>84.7% — remains institute property (tab 03)</t>
+          <t>92.6% — remains institute property (tab 03)</t>
         </is>
       </c>
     </row>
@@ -679,20 +679,20 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>125971</v>
+        <v>54523</v>
       </c>
       <c r="C8" s="9" t="inlineStr"/>
       <c r="D8" s="9" t="inlineStr"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>15.3% — the true unrecoverable cost (tab 04)</t>
+          <t>7.4% — the true unrecoverable cost (tab 04)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>WHY THIS IS NOT AN 8.24 LAKH EXPENSE</t>
+          <t>WHY THIS IS NOT A 7.38 LAKH EXPENSE</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>3.  The first decision is 2.90 L, not 8.24 L. Release is gated on demonstrated milestones, and the committee re-decides at each gate. See tab 06.</t>
+          <t>3.  The first decision is 2.90 L, not 7.38 L. Release is gated on demonstrated milestones, and the committee re-decides at each gate. See tab 06.</t>
         </is>
       </c>
     </row>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>824072</v>
+        <v>737829</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>0.6995090283106635</v>
+        <v>0.6669164416733178</v>
       </c>
       <c r="D18" s="9" t="inlineStr"/>
       <c r="E18" s="9" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>354000</v>
+        <v>368500</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.3004909716893365</v>
+        <v>0.3330835583266822</v>
       </c>
       <c r="D19" s="9" t="inlineStr"/>
       <c r="E19" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>1178072</v>
+        <v>1106329</v>
       </c>
       <c r="C20" s="18" t="n">
         <v>1</v>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B22" s="20" t="n">
-        <v>316770</v>
+        <v>373630</v>
       </c>
       <c r="C22" s="19" t="inlineStr"/>
       <c r="D22" s="19" t="inlineStr"/>
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -956,7 +956,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Soldering station</t>
+          <t>Equipment cases</t>
         </is>
       </c>
       <c r="B10" s="14" t="n">
@@ -964,18 +964,18 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Department facility</t>
+          <t>Institute facility</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Rotary tool + CF extraction</t>
+          <t>Soldering station</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>8500</v>
+        <v>9000</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Bench power supply</t>
+          <t>Rotary tool + CF extraction</t>
         </is>
       </c>
       <c r="B12" s="14" t="n">
@@ -1001,30 +1001,75 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
+          <t>Bench power supply</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Department facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
           <t>Multimeters</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B14" s="14" t="n">
         <v>8000</v>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Department facility</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Fire extinguisher, sand, charging bags</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Institute facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Charger PSU</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Institute facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>TOTAL INSTITUTIONAL CONTRIBUTION</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
-        <v>354000</v>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>30.0% of total programme value</t>
+      <c r="B17" s="17" t="n">
+        <v>368500</v>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>33.3% of total programme value</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1170,149 +1215,74 @@
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>Charger PSU</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>Any electronics lab</t>
-        </is>
-      </c>
-      <c r="E8" s="25" t="inlineStr">
-        <is>
-          <t>12 V at 20 A or better. The bench supply was already counted as institutional; this is the field equivalent.</t>
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Battery chargers</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Robotics / aeromodelling club</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Does it balance-charge 6S Li-ion at 5 A+, and measure per-cell internal resistance? If it does, the separate cell tester stays deleted.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>Battery chargers</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="n">
-        <v>14000</v>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>Robotics / aeromodelling club</t>
-        </is>
-      </c>
-      <c r="E9" s="26" t="inlineStr">
-        <is>
-          <t>Does it balance-charge 6S Li-ion at 5 A+, and measure per-cell internal resistance? If it does, the separate cell tester stays deleted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>Equipment cases</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n">
-        <v>9000</v>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr">
-        <is>
-          <t>Department stores</t>
-        </is>
-      </c>
-      <c r="E10" s="26" t="inlineStr">
-        <is>
-          <t>Foam-lined crates that survive transport to the competition venue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>Fire extinguisher, sand, charging bags</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="inlineStr">
-        <is>
-          <t>Institute safety office</t>
-        </is>
-      </c>
-      <c r="E11" s="26" t="inlineStr">
-        <is>
-          <t>Class D or CO2 rated for lithium, and may it be signed out to a field site? 54 cells are cycled across this programme.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>RTK base receiver</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B9" s="14" t="n">
         <v>18000</v>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>CHECK</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Civil Engineering DGPS</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>HIGHEST VALUE, LEAST LIKELY TO JUST WORK. Does it output RTCM3 corrections at 1 Hz to a third-party rover, and is it free during the flight window? A total station is not a substitute.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>MAXIMUM REDUCTION IF ALL ARE HELD</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
-        <v>70500</v>
-      </c>
-      <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>Request falls from 8.24 L to about 7.43 L, and the institutional contribution rises correspondingly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="B10" s="17" t="n">
+        <v>56000</v>
+      </c>
+      <c r="C10" s="16" t="inlineStr"/>
+      <c r="D10" s="16" t="inlineStr"/>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Would take the request from 7.38 L to about 6.66 L. Items already confirmed held are NOT listed above -- that reduction is already inside the 7.38 L figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Ask the specific question, not the general one. "Do you have a GPS?" gets a yes that turns out to be a total station. Each row above names the property that decides whether the item is actually usable for this project.</t>
         </is>
@@ -1321,8 +1291,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1334,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1442,11 +1412,11 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Equipment cases</t>
+          <t>Safety-pilot transmitter</t>
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
@@ -1455,18 +1425,18 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Transport and storage for any field campaign.</t>
+          <t>Reusable across every future UAV built by the department.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Fire extinguisher, sand, charging bags</t>
+          <t>Sun hood + observer monitor</t>
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
@@ -1475,14 +1445,14 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Permanent lab safety equipment.</t>
+          <t>Field equipment.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Safety-pilot transmitter</t>
+          <t>Thrust stand</t>
         </is>
       </c>
       <c r="B10" s="14" t="n">
@@ -1490,43 +1460,43 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Ground segment</t>
+          <t>Test equipment</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Reusable across every future UAV built by the department.</t>
+          <t>Calibrated propulsion test instrument; reusable for every future rotor or propeller study.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Sun hood + observer monitor</t>
+          <t>Battery chargers</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>1500</v>
+        <v>14000</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Ground segment</t>
+          <t>Test equipment</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Field equipment.</t>
+          <t>General lab charging for all battery-powered student projects.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Thrust stand</t>
+          <t>Calibrated scale + remaining</t>
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
@@ -1535,95 +1505,35 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Calibrated propulsion test instrument; reusable for every future rotor or propeller study.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Battery chargers</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>14000</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Test equipment</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>General lab charging for all battery-powered student projects.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Charger PSU</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Test equipment</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>General bench supply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Calibrated scale + remaining</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Test equipment</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
           <t>General laboratory instrument.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>SUBTOTAL, capital (before duty, GST and contingency)</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
-        <v>553400</v>
-      </c>
-      <c r="C16" s="16" t="inlineStr"/>
-      <c r="D16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="B13" s="17" t="n">
+        <v>538900</v>
+      </c>
+      <c r="C13" s="16" t="inlineStr"/>
+      <c r="D13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>With duty, GST and contingency apportioned</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
-        <v>698101</v>
-      </c>
-      <c r="C17" s="7" t="inlineStr"/>
-      <c r="D17" s="28" t="inlineStr">
-        <is>
-          <t>84.7% of the total request</t>
+      <c r="B14" s="8" t="n">
+        <v>683306</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>92.6% of the total request</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1684,131 +1594,71 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Relief kits (14)</t>
+          <t>Remaining ground items</t>
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>5600</v>
+        <v>25000</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Rule C6 fixes the kit at 200 g.</t>
+          <t>Cables, mounts, field consumables. RTCM corrections ride the existing telemetry link, so no separate base-to-rover radio is carried.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Ground-truth apparatus</t>
+          <t>Fasteners, tape, connectors, filament</t>
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>4860</v>
+        <v>13000</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>R5. Mannequins, mats, markers, clothing and dummy kits all fabricated. Dummy kits and clothing are BETTER made than bought -- exact 200 g mass, and wi</t>
+          <t>KEEP.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Remaining ground items</t>
+          <t>DGCA registration</t>
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Cables, mounts, field consumables. RTCM corrections ride the existing telemetry link, so no separate base-to-rover radio is carried.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Spare airframe structure set</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>25000</v>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>KEEP. What a crash consumes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Spare propellers, plate and tube stock</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>21400</v>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>KEEP. Consumables.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Fasteners, tape, connectors, filament</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>13000</v>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>KEEP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>DGCA registration</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
           <t>KEEP. At 6.36 kg these are Small category (2-25 kg) under the Drone Rules 2021 -- only Nano is broadly exempt. UIN registration is required.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>SUBTOTAL, consumable</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>99860</v>
-      </c>
-      <c r="C12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="B8" s="17" t="n">
+        <v>43000</v>
+      </c>
+      <c r="C8" s="16" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>With duty, GST and contingency apportioned</t>
         </is>
       </c>
-      <c r="B13" s="30" t="n">
-        <v>125971</v>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t>15.3% of the request — the genuine cost of competing</t>
+      <c r="B9" s="30" t="n">
+        <v>54523</v>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>7.4% of the request — the genuine cost of competing</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2515,7 @@
       </c>
       <c r="C9" s="16" t="inlineStr"/>
       <c r="D9" s="17" t="n">
-        <v>824072</v>
+        <v>737829</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
@@ -2696,7 +2546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2828,50 +2678,110 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Spare compute module</t>
+          <t>Spare airframe structure set</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Removes a single point of failure</t>
+          <t>Deferred 2026-08-18. Was the crash cover; one hard landing now ends the campaign</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
+          <t>Spare propellers and stock</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>21400</v>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Deferred 2026-08-18. Propellers are the most consumed item in flight test</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Spare compute module</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Removes a single point of failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
           <t>Field data campaign</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B14" s="14" t="n">
         <v>15000</v>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Detection recall measured rather than modelled</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Relief kits (14)</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>5600</v>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Deferred 2026-08-18. THE DELIVERED PAYLOAD. Rule C6 fixes it at 200 g; without kits there is nothing to release and the delivery task scores nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Ground-truth apparatus</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>4860</v>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Deferred 2026-08-18. Detection recall now has no target to be measured against</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>TOTAL DEFERRED</t>
         </is>
       </c>
-      <c r="B13" s="30" t="n">
-        <v>316770</v>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="B17" s="30" t="n">
+        <v>373630</v>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>Capability given up to reduce this request.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="34" t="inlineStr">
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>ONE ITEM NEEDS A DECISION FROM THE INSTITUTE, NOT FROM US: third-party insurance was deferred at the team's direction, but cover is commonly mandatory for unmanned operations in India. It must be confirmed against the DGCA rules and the competition rulebook BEFORE ANY FLIGHT. If it is required it ceases to be a budget choice, and 25,000 returns to the request.</t>
         </is>
@@ -2880,7 +2790,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2974,7 +2884,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>If the institution already owns it, it is not in the request. This removed 354,000 (tab 01). Tab 02 lists what still needs checking.</t>
+          <t>If the institution already owns it, it is not in the request. This removed 368,500 (tab 01). Tab 02 lists what still needs checking.</t>
         </is>
       </c>
     </row>

--- a/hardware/bom/RescueSwarm_University_Funding_Request.xlsx
+++ b/hardware/bom/RescueSwarm_University_Funding_Request.xlsx
@@ -608,7 +608,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NIDAR 2026-27, Track 1  ·  Thapar Institute of Engineering and Technology  ·  Rev A, 2026-08-18  ·  GENERATED FILE — run hardware/bom/build_university_request.py</t>
+          <t>NIDAR 2026-27, Track 1  ·  Thapar Institute of Engineering and Technology  ·  Rev A, 2026-08-21  ·  GENERATED FILE — run hardware/bom/build_university_request.py</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>737829</v>
+        <v>734379</v>
       </c>
       <c r="C6" s="7" t="inlineStr"/>
       <c r="D6" s="7" t="inlineStr"/>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>683306</v>
+        <v>679830</v>
       </c>
       <c r="C7" s="9" t="inlineStr"/>
       <c r="D7" s="9" t="inlineStr"/>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>54523</v>
+        <v>54549</v>
       </c>
       <c r="C8" s="9" t="inlineStr"/>
       <c r="D8" s="9" t="inlineStr"/>
@@ -692,7 +692,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>WHY THIS IS NOT A 7.38 LAKH EXPENSE</t>
+          <t>WHY THIS IS NOT A 7.34 LAKH EXPENSE</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>3.  The first decision is 2.90 L, not 7.38 L. Release is gated on demonstrated milestones, and the committee re-decides at each gate. See tab 06.</t>
+          <t>3.  The first decision is 2.90 L, not 7.34 L. Release is gated on demonstrated milestones, and the committee re-decides at each gate. See tab 06.</t>
         </is>
       </c>
     </row>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>737829</v>
+        <v>734379</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>0.6669164416733178</v>
+        <v>0.6658744975650094</v>
       </c>
       <c r="D18" s="9" t="inlineStr"/>
       <c r="E18" s="9" t="inlineStr">
@@ -779,7 +779,7 @@
         <v>368500</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.3330835583266822</v>
+        <v>0.3341255024349906</v>
       </c>
       <c r="D19" s="9" t="inlineStr"/>
       <c r="E19" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>1106329</v>
+        <v>1102879</v>
       </c>
       <c r="C20" s="18" t="n">
         <v>1</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>33.3% of total programme value</t>
+          <t>33.4% of total programme value</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       <c r="D10" s="16" t="inlineStr"/>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>Would take the request from 7.38 L to about 6.66 L. Items already confirmed held are NOT listed above -- that reduction is already inside the 7.38 L figure.</t>
+          <t>Would take the request from 7.34 L to about 6.63 L. Items already confirmed held are NOT listed above -- that reduction is already inside the 7.34 L figure.</t>
         </is>
       </c>
     </row>
@@ -1352,11 +1352,11 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Air vehicles, 3 x 157,800</t>
+          <t>Air vehicles, 3 x 156,800</t>
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>473400</v>
+        <v>470400</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>538900</v>
+        <v>535900</v>
       </c>
       <c r="C13" s="16" t="inlineStr"/>
       <c r="D13" s="16" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>683306</v>
+        <v>679830</v>
       </c>
       <c r="C14" s="7" t="inlineStr"/>
       <c r="D14" s="28" t="inlineStr">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="B9" s="30" t="n">
-        <v>54523</v>
+        <v>54549</v>
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1693,7 +1693,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Air vehicle bill of materials — 157,800 per aircraft, 3 required</t>
+          <t>Air vehicle bill of materials — 156,800 per aircraft, 3 required</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>AI accelerator</t>
+          <t>Companion computer</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>Edge AI module, &gt;=20 TOPS</t>
+          <t>Raspberry Pi 5 8 GB. THE HOST THE AUTONOMY RUNS ON -- Linux, ROS 2, th</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -1803,14 +1803,14 @@
         <v>1</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>20000</v>
-      </c>
-      <c r="H6" s="32" t="inlineStr">
-        <is>
-          <t>e-con Systems (Chennai)</t>
+        <v>8000</v>
+      </c>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>To be quoted</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>GNSS RTK primary</t>
+          <t>AI accelerator</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>AeroNav-series NavIC L1+L5 RTK</t>
+          <t>Edge AI module. REQUIREMENT IS THROUGHPUT, NOT TOPS: &gt;=37 inferences/s at 640x640 INT8 (12 tiles at 3.06 Hz). PCIe attach; USB accelerators do not reach it.</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -1837,82 +1837,82 @@
         <v>1</v>
       </c>
       <c r="F7" s="24" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>11000</v>
+      </c>
+      <c r="H7" s="32" t="inlineStr">
+        <is>
+          <t>e-con Systems (Chennai)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>GNSS RTK primary</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>RTK-capable receiver: must accept RTCM3 corrections and report an RTK FIXED solution at &lt;=3 cm CEP. SBAS-corrected receivers at ~1.5 m CEP DO NOT MEET THIS regardless of what the part is named -- confirm against the datasheet, not the product title.</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="24" t="n">
         <v>18000</v>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G8" s="24" t="n">
         <v>18000</v>
       </c>
-      <c r="H7" s="32" t="inlineStr">
+      <c r="H8" s="32" t="inlineStr">
         <is>
           <t>Teravolt Labs (India)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="9" t="n">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Motors</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>5008-class, 340 KV, 6S, 18 in prop. MUST deliver &gt;=3.18 kgf static per motor with hover at 1.59 kgf (50% of max); published thrust curve required, or thrust-stand verified before fleet commitment. &lt;=175 g.</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>hobby</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>5008-class, 340 KV</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>hobby</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="14" t="n">
+      <c r="F9" s="14" t="n">
         <v>4500</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G9" s="14" t="n">
         <v>18000</v>
       </c>
-      <c r="H8" s="33" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>Reflex Drive (Lucknow) or equivalent</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>Li-ion cells</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>21700 NMC, &gt;=4000 mAh, 40-45 A</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>KEEP</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>700</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>12600</v>
-      </c>
-      <c r="H9" s="32" t="inlineStr">
-        <is>
-          <t>GODI India (Hyderabad)</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Li-ion cells</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>CF tube, plate and machined clamps</t>
+          <t>21700 NMC, 4500 mAh min, 45 A continuous unrestricted (no 80C cut-off), DC-IR &lt;=15 mOhm @50% SoC 25C, &lt;=72 g</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -1936,17 +1936,17 @@
         </is>
       </c>
       <c r="E10" s="23" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>13000</v>
+        <v>700</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>13000</v>
+        <v>12600</v>
       </c>
       <c r="H10" s="32" t="inlineStr">
         <is>
-          <t>Kineco Kaman (Goa) + institute machine shop</t>
+          <t>GODI India (Hyderabad)</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>Camera + lens</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>Arducam IMX477 + 6 mm S-mount</t>
+          <t>CF tube, plate and machined clamps</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -1973,48 +1973,48 @@
         <v>1</v>
       </c>
       <c r="F11" s="24" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>13000</v>
+      </c>
+      <c r="H11" s="32" t="inlineStr">
+        <is>
+          <t>Kineco Kaman (Goa) + institute machine shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Camera + lens</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Arducam IMX477 (type 1/2.3, 1.55 um) + 6 mm CS lens, FIXED FOCUS. Hyperfocal is 4.15 m against a 30 m minimum altitude, so a focus motor buys nothing and adds a moving part.</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="24" t="n">
         <v>11100</v>
       </c>
-      <c r="G11" s="24" t="n">
+      <c r="G12" s="24" t="n">
         <v>11100</v>
       </c>
-      <c r="H11" s="32" t="inlineStr">
+      <c r="H12" s="32" t="inlineStr">
         <is>
           <t>Indian distributor</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Pack, BMS, PDB, BEC</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>6S3P pack, BMS, PDB, BEC</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>hobby</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>8500</v>
-      </c>
-      <c r="G12" s="14" t="n">
-        <v>8500</v>
-      </c>
-      <c r="H12" s="33" t="inlineStr">
-        <is>
-          <t>Flameback Tech (Baddi, HP)</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>RC rx, storage, cooling, mounts</t>
+          <t>Pack, BMS, PDB, BEC</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>ExpressLRS 2.4 GHz rx (3.5+, native MAVLink)</t>
+          <t>6S3P pack, BMS, PDB, BEC</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H13" s="33" t="inlineStr">
         <is>
-          <t>Zerodrag (India)</t>
+          <t>Flameback Tech (Baddi, HP)</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>ESCs</t>
+          <t>RC rx, storage, cooling, mounts</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>60 A, field-oriented</t>
+          <t>ExpressLRS 2.4 GHz rx (3.5+, native MAVLink)</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -2072,17 +2072,17 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1800</v>
+        <v>8500</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>7200</v>
+        <v>8500</v>
       </c>
       <c r="H14" s="33" t="inlineStr">
         <is>
-          <t>Reflex Drive (Lucknow)</t>
+          <t>Zerodrag (India)</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Mesh node + antennas</t>
+          <t>ESCs</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>5.8 GHz mesh node</t>
+          <t>50-60 A continuous, field-oriented, 6S. Peak demand is 29 A per motor at T/W 2.0.</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -2106,17 +2106,17 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>6000</v>
+        <v>1800</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="H15" s="33" t="inlineStr">
         <is>
-          <t>FxUAV Technologies (Burla)</t>
+          <t>Reflex Drive (Lucknow)</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Payload system</t>
+          <t>Mesh node + antennas</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Servo release, 4 stations</t>
+          <t>5.8 GHz mesh node</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -2143,14 +2143,14 @@
         <v>1</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="H16" s="33" t="inlineStr">
         <is>
-          <t>Zerodrag + in-house</t>
+          <t>FxUAV Technologies (Burla)</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Propellers</t>
+          <t>Payload system</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>18 in carbon</t>
+          <t>Servo release, 4 stations</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -2174,17 +2174,17 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1000</v>
+        <v>4500</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="H17" s="33" t="inlineStr">
         <is>
-          <t>Reflex Drive / UAV Garage</t>
+          <t>Zerodrag + in-house</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2194,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Wiring, connectors</t>
+          <t>Propellers</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Silicone wire, XT90-S, JST-GH</t>
+          <t>18 in carbon</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -2208,17 +2208,17 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>2400</v>
+        <v>1000</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2400</v>
+        <v>4000</v>
       </c>
       <c r="H18" s="33" t="inlineStr">
         <is>
-          <t>Polycab / Robu</t>
+          <t>Reflex Drive / UAV Garage</t>
         </is>
       </c>
     </row>
@@ -2228,89 +2228,107 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
+          <t>Wiring, connectors</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Silicone wire, XT90-S, JST-GH</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>hobby</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H19" s="33" t="inlineStr">
+        <is>
+          <t>Polycab / Robu</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
           <t>Prop adapters</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>6 mm self-tightening hub</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>hobby</t>
         </is>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F20" s="14" t="n">
         <v>350</v>
       </c>
-      <c r="G19" s="14" t="n">
+      <c r="G20" s="14" t="n">
         <v>1400</v>
       </c>
-      <c r="H19" s="33" t="inlineStr">
+      <c r="H20" s="33" t="inlineStr">
         <is>
           <t>Reflex Drive</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>VEGA co-processor</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t>C-DAC VEGA ARIES v3.0</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E21" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F21" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G21" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="32" t="inlineStr">
+      <c r="H21" s="32" t="inlineStr">
         <is>
           <t>C-DAC (free to top-100 teams)</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr"/>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>PER AIRCRAFT</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr"/>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="16" t="inlineStr"/>
-      <c r="F21" s="17" t="inlineStr"/>
-      <c r="G21" s="17" t="n">
-        <v>157800</v>
-      </c>
-      <c r="H21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr"/>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>FLEET OF 3</t>
+          <t>PER AIRCRAFT</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr"/>
@@ -2318,40 +2336,56 @@
       <c r="E22" s="16" t="inlineStr"/>
       <c r="F22" s="17" t="inlineStr"/>
       <c r="G22" s="17" t="n">
-        <v>473400</v>
+        <v>156800</v>
       </c>
       <c r="H22" s="16" t="inlineStr"/>
     </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>A fully specified variant of this aircraft was costed at 2,90,546 per unit using named, verified Indian parts throughout (RescueSwarm_BOM_India_Verified.xlsx). The configuration above adopts generic hobby-grade propulsion and ancillaries where the specification is easy to verify on receipt, which is what brings it to 157,800. Motor thrust is unpublished at this grade and is verified on the thrust stand before first flight.</t>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr"/>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>FLEET OF 3</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr"/>
+      <c r="D23" s="16" t="inlineStr"/>
+      <c r="E23" s="16" t="inlineStr"/>
+      <c r="F23" s="17" t="inlineStr"/>
+      <c r="G23" s="17" t="n">
+        <v>470400</v>
+      </c>
+      <c r="H23" s="16" t="inlineStr"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>A fully specified variant of this aircraft was costed at 2,90,546 per unit using named, verified Indian parts throughout (RescueSwarm_BOM_India_Verified.xlsx). The configuration above adopts generic hobby-grade propulsion and ancillaries where the specification is easy to verify on receipt, which is what brings it to 156,800. Motor thrust is unpublished at this grade and is verified on the thrust stand before first flight.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2515,7 +2549,7 @@
       </c>
       <c r="C9" s="16" t="inlineStr"/>
       <c r="D9" s="17" t="n">
-        <v>737829</v>
+        <v>734379</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>

--- a/hardware/bom/RescueSwarm_University_Funding_Request.xlsx
+++ b/hardware/bom/RescueSwarm_University_Funding_Request.xlsx
@@ -608,7 +608,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NIDAR 2026-27, Track 1  ·  Thapar Institute of Engineering and Technology  ·  Rev A, 2026-08-21  ·  GENERATED FILE — run hardware/bom/build_university_request.py</t>
+          <t>NIDAR 2026-27, Track 1  ·  Thapar Institute of Engineering and Technology  ·  Rev A, 2026-08-22  ·  GENERATED FILE — run hardware/bom/build_university_request.py</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>734379</v>
+        <v>743004</v>
       </c>
       <c r="C6" s="7" t="inlineStr"/>
       <c r="D6" s="7" t="inlineStr"/>
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>679830</v>
+        <v>688520</v>
       </c>
       <c r="C7" s="9" t="inlineStr"/>
       <c r="D7" s="9" t="inlineStr"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>92.6% — remains institute property (tab 03)</t>
+          <t>92.7% — remains institute property (tab 03)</t>
         </is>
       </c>
     </row>
@@ -679,20 +679,20 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>54549</v>
+        <v>54484</v>
       </c>
       <c r="C8" s="9" t="inlineStr"/>
       <c r="D8" s="9" t="inlineStr"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>7.4% — the true unrecoverable cost (tab 04)</t>
+          <t>7.3% — the true unrecoverable cost (tab 04)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>WHY THIS IS NOT A 7.34 LAKH EXPENSE</t>
+          <t>WHY THIS IS NOT A 7.43 LAKH EXPENSE</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>3.  The first decision is 2.90 L, not 7.34 L. Release is gated on demonstrated milestones, and the committee re-decides at each gate. See tab 06.</t>
+          <t>3.  The first decision is 2.90 L, not 7.43 L. Release is gated on demonstrated milestones, and the committee re-decides at each gate. See tab 06.</t>
         </is>
       </c>
     </row>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>734379</v>
+        <v>743004</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>0.6658744975650094</v>
+        <v>0.6684672299874764</v>
       </c>
       <c r="D18" s="9" t="inlineStr"/>
       <c r="E18" s="9" t="inlineStr">
@@ -779,7 +779,7 @@
         <v>368500</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>0.3341255024349906</v>
+        <v>0.3315327700125236</v>
       </c>
       <c r="D19" s="9" t="inlineStr"/>
       <c r="E19" s="9" t="inlineStr">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>1102879</v>
+        <v>1111504</v>
       </c>
       <c r="C20" s="18" t="n">
         <v>1</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>33.4% of total programme value</t>
+          <t>33.2% of total programme value</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       <c r="D10" s="16" t="inlineStr"/>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>Would take the request from 7.34 L to about 6.63 L. Items already confirmed held are NOT listed above -- that reduction is already inside the 7.34 L figure.</t>
+          <t>Would take the request from 7.43 L to about 6.71 L. Items already confirmed held are NOT listed above -- that reduction is already inside the 7.43 L figure.</t>
         </is>
       </c>
     </row>
@@ -1352,11 +1352,11 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Air vehicles, 3 x 156,800</t>
+          <t>Air vehicles, 3 x 159,300</t>
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>470400</v>
+        <v>477900</v>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>535900</v>
+        <v>543400</v>
       </c>
       <c r="C13" s="16" t="inlineStr"/>
       <c r="D13" s="16" t="inlineStr"/>
@@ -1528,12 +1528,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>679830</v>
+        <v>688520</v>
       </c>
       <c r="C14" s="7" t="inlineStr"/>
       <c r="D14" s="28" t="inlineStr">
         <is>
-          <t>92.6% of the total request</t>
+          <t>92.7% of the total request</t>
         </is>
       </c>
     </row>
@@ -1654,11 +1654,11 @@
         </is>
       </c>
       <c r="B9" s="30" t="n">
-        <v>54549</v>
+        <v>54484</v>
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
-          <t>7.4% of the request — the genuine cost of competing</t>
+          <t>7.3% of the request — the genuine cost of competing</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Air vehicle bill of materials — 156,800 per aircraft, 3 required</t>
+          <t>Air vehicle bill of materials — 159,300 per aircraft, 3 required</t>
         </is>
       </c>
     </row>
@@ -2211,10 +2211,10 @@
         <v>4</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1000</v>
+        <v>1625</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4000</v>
+        <v>6500</v>
       </c>
       <c r="H18" s="33" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
       <c r="E22" s="16" t="inlineStr"/>
       <c r="F22" s="17" t="inlineStr"/>
       <c r="G22" s="17" t="n">
-        <v>156800</v>
+        <v>159300</v>
       </c>
       <c r="H22" s="16" t="inlineStr"/>
     </row>
@@ -2352,14 +2352,14 @@
       <c r="E23" s="16" t="inlineStr"/>
       <c r="F23" s="17" t="inlineStr"/>
       <c r="G23" s="17" t="n">
-        <v>470400</v>
+        <v>477900</v>
       </c>
       <c r="H23" s="16" t="inlineStr"/>
     </row>
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>A fully specified variant of this aircraft was costed at 2,90,546 per unit using named, verified Indian parts throughout (RescueSwarm_BOM_India_Verified.xlsx). The configuration above adopts generic hobby-grade propulsion and ancillaries where the specification is easy to verify on receipt, which is what brings it to 156,800. Motor thrust is unpublished at this grade and is verified on the thrust stand before first flight.</t>
+          <t>A fully specified variant of this aircraft was costed at 2,90,546 per unit using named, verified Indian parts throughout (RescueSwarm_BOM_India_Verified.xlsx). The configuration above adopts generic hobby-grade propulsion and ancillaries where the specification is easy to verify on receipt, which is what brings it to 159,300. Motor thrust is unpublished at this grade and is verified on the thrust stand before first flight.</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C9" s="16" t="inlineStr"/>
       <c r="D9" s="17" t="n">
-        <v>734379</v>
+        <v>743004</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
